--- a/tumores/Metástasis cervical de origen desconocido.xlsx
+++ b/tumores/Metástasis cervical de origen desconocido.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32F57D3-D230-406A-81AA-8BD625AD8660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C4F9B-6640-4FF3-9E0F-C777F02C9AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="8520" windowHeight="8880" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="103">
   <si>
     <t>T</t>
   </si>
@@ -148,15 +148,9 @@
     <t>Ganglios bilaterales ≤6 cm</t>
   </si>
   <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>N3a</t>
   </si>
   <si>
-    <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>N3b</t>
   </si>
   <si>
@@ -175,21 +169,6 @@
     <t>Bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Un ganglio ipsilateral &gt;3 cm , Multiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
-  </si>
-  <si>
-    <t>Unilateral cervical &lt;6cm</t>
-  </si>
-  <si>
-    <t>Unilateral cervical &gt;6cm</t>
-  </si>
-  <si>
-    <t>Bilateral cervical &gt;6cm</t>
-  </si>
-  <si>
-    <t>Debajo del cricoides</t>
-  </si>
-  <si>
     <t>IVA</t>
   </si>
   <si>
@@ -223,15 +202,6 @@
     <t>Ninguno</t>
   </si>
   <si>
-    <t xml:space="preserve">Bilateral retrofaringea &lt;6cm, encima del cricoides. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilateral retrofaringea &lt;6cm, encima del cricoides. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilateral cervical &lt;6cm, encima del cricoides. </t>
-  </si>
-  <si>
     <t>N2, N2a, N2b, N2c</t>
   </si>
   <si>
@@ -248,9 +218,6 @@
   </si>
   <si>
     <t>🟩 N1: Ganglio/s ipsilateral ≤6 cm *</t>
-  </si>
-  <si>
-    <t>🟩 N1: Metastasis en 4 o menos ganglios</t>
   </si>
   <si>
     <t>🟩 N1: Un ganglio ipsilateral ≤3 cm y ENE-</t>
@@ -350,9 +317,6 @@
     <t>🟦 N3: Diseminación por debajo del borde inferior del cricoides</t>
   </si>
   <si>
-    <t>🟦 N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t xml:space="preserve">🟦 N3b: Ganglios con ENE+ </t>
   </si>
   <si>
@@ -363,6 +327,60 @@
   </si>
   <si>
     <t>M1: Metástasis a distancia</t>
+  </si>
+  <si>
+    <t>🟦 N3a: Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios &gt;6 cm</t>
+  </si>
+  <si>
+    <t>Metástasis en 4 o menos ganglios</t>
+  </si>
+  <si>
+    <t>🟩 N1: Metástasis en 4 o menos ganglios</t>
+  </si>
+  <si>
+    <t>Metástasis en más de 4 ganglios</t>
+  </si>
+  <si>
+    <t>🟨 N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟨 N2: Metástasis en más de 4 ganglios</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &lt;6cm</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>M.Unilateral G.cervicales &gt;6cm</t>
+  </si>
+  <si>
+    <t>M.Bilateral G.cervicales &gt;6cm</t>
+  </si>
+  <si>
+    <t>Disem. Debajo del borde inferior del cricoides</t>
+  </si>
+  <si>
+    <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
   </si>
 </sst>
 </file>
@@ -1096,11 +1114,11 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
@@ -1115,11 +1133,11 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
@@ -1134,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="1" t="s">
@@ -1153,11 +1171,11 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
@@ -1172,11 +1190,11 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="1" t="s">
@@ -1191,11 +1209,11 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="6" t="s">
@@ -1210,13 +1228,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>9</v>
@@ -1230,13 +1248,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>10</v>
@@ -1250,13 +1268,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>27</v>
@@ -1273,13 +1291,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>29</v>
@@ -1293,13 +1311,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>29</v>
@@ -1313,19 +1331,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1333,13 +1351,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>9</v>
@@ -1353,13 +1371,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>10</v>
@@ -1373,19 +1391,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -1393,20 +1411,20 @@
         <v>6</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="14" t="s">
-        <v>15</v>
+      <c r="G17" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="11" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1414,13 +1432,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
@@ -1435,13 +1453,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
@@ -1456,13 +1474,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
@@ -1477,13 +1495,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -1497,13 +1515,13 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>36</v>
@@ -1517,13 +1535,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -1537,13 +1555,13 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -1552,24 +1570,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1577,19 +1595,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,13 +1615,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>9</v>
@@ -1617,13 +1635,13 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>10</v>
@@ -1637,13 +1655,13 @@
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>11</v>
@@ -1657,22 +1675,22 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1680,19 +1698,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1700,19 +1718,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1720,39 +1738,39 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1760,19 +1778,19 @@
         <v>6</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>15</v>
@@ -1783,13 +1801,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>9</v>
@@ -1803,13 +1821,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>10</v>
@@ -1823,13 +1841,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>27</v>
@@ -1846,13 +1864,13 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>29</v>
@@ -1866,13 +1884,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>29</v>
@@ -1886,19 +1904,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1906,13 +1924,13 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>9</v>
@@ -1926,13 +1944,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>10</v>
@@ -1946,19 +1964,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1966,20 +1984,20 @@
         <v>6</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G45" s="14" t="s">
-        <v>15</v>
+      <c r="G45" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1987,7 +2005,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>7</v>
@@ -2007,13 +2025,13 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>10</v>
@@ -2027,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>11</v>
@@ -2047,13 +2065,13 @@
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>33</v>
@@ -2067,13 +2085,13 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>36</v>
@@ -2087,13 +2105,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>38</v>
@@ -2107,13 +2125,13 @@
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>38</v>
@@ -2122,24 +2140,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2147,19 +2165,19 @@
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2167,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>8</v>
@@ -2187,13 +2205,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>10</v>
@@ -2207,13 +2225,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>11</v>
@@ -2227,22 +2245,22 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2250,13 +2268,13 @@
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>36</v>
@@ -2270,19 +2288,19 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2290,39 +2308,39 @@
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -2330,19 +2348,19 @@
         <v>6</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>15</v>
@@ -2353,10 +2371,10 @@
         <v>6</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
@@ -2371,10 +2389,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
@@ -2389,10 +2407,10 @@
         <v>6</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>27</v>
@@ -2401,7 +2419,7 @@
         <v>11</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2409,10 +2427,10 @@
         <v>6</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>27</v>
@@ -2421,7 +2439,7 @@
         <v>11</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2429,10 +2447,10 @@
         <v>6</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>27</v>
@@ -2441,7 +2459,7 @@
         <v>11</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2449,10 +2467,10 @@
         <v>6</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>27</v>
@@ -2461,7 +2479,7 @@
         <v>29</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2469,17 +2487,17 @@
         <v>6</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2487,17 +2505,17 @@
         <v>6</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2505,18 +2523,18 @@
         <v>6</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -2524,13 +2542,13 @@
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>9</v>
@@ -2544,13 +2562,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>10</v>
@@ -2564,13 +2582,13 @@
         <v>6</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>11</v>
@@ -2584,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>33</v>
@@ -2604,13 +2622,13 @@
         <v>6</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>36</v>
@@ -2624,13 +2642,13 @@
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>38</v>
@@ -2644,13 +2662,13 @@
         <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>38</v>
@@ -2659,24 +2677,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -2684,19 +2702,19 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -2704,13 +2722,13 @@
         <v>6</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>9</v>
@@ -2724,13 +2742,13 @@
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C83" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>10</v>
@@ -2744,13 +2762,13 @@
         <v>6</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>11</v>
@@ -2764,22 +2782,22 @@
         <v>6</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -2787,19 +2805,19 @@
         <v>6</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -2807,19 +2825,19 @@
         <v>6</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -2827,39 +2845,39 @@
         <v>6</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -2867,19 +2885,19 @@
         <v>6</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C90" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>15</v>
@@ -2891,16 +2909,16 @@
         <v>16</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
@@ -2908,18 +2926,18 @@
         <v>16</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C92" s="12"/>
       <c r="D92" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -2927,16 +2945,16 @@
         <v>16</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
@@ -2944,18 +2962,18 @@
         <v>16</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C94" s="12"/>
       <c r="D94" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
@@ -2963,16 +2981,16 @@
         <v>16</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -2980,18 +2998,18 @@
         <v>16</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C96" s="16"/>
       <c r="D96" s="16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E96" s="16"/>
       <c r="F96" s="16" t="s">
         <v>18</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -2999,18 +3017,18 @@
         <v>16</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C97" s="18"/>
       <c r="D97" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E97" s="18"/>
       <c r="F97" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -3018,18 +3036,18 @@
         <v>16</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C98" s="12"/>
       <c r="D98" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3037,18 +3055,18 @@
         <v>16</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C99" s="18"/>
       <c r="D99" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E99" s="18"/>
       <c r="F99" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3056,18 +3074,18 @@
         <v>16</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C100" s="12"/>
       <c r="D100" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3075,18 +3093,18 @@
         <v>16</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C101" s="18"/>
       <c r="D101" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E101" s="18"/>
       <c r="F101" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -3094,18 +3112,18 @@
         <v>16</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C102" s="12"/>
       <c r="D102" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -3221,13 +3239,13 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -3235,13 +3253,13 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3255,7 +3273,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">

--- a/tumores/Metástasis cervical de origen desconocido.xlsx
+++ b/tumores/Metástasis cervical de origen desconocido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C4F9B-6640-4FF3-9E0F-C777F02C9AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505DD67A-604D-4843-BBCB-11939A4FD137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="97">
   <si>
     <t>T</t>
   </si>
@@ -55,24 +55,12 @@
     <t>Patológico</t>
   </si>
   <si>
-    <t>NX</t>
-  </si>
-  <si>
-    <t>N0</t>
-  </si>
-  <si>
     <t>N1</t>
   </si>
   <si>
-    <t>Ganglios no evaluables</t>
-  </si>
-  <si>
     <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
-    <t>Sin metástasis en ganglios</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ENE+: </t>
   </si>
   <si>
@@ -209,12 +197,6 @@
   </si>
   <si>
     <t>T0: Tumor primario no evaluable</t>
-  </si>
-  <si>
-    <t>NX: Ganglios no evaluables</t>
-  </si>
-  <si>
-    <t>N0: Ganglios sin metástasis</t>
   </si>
   <si>
     <t>🟩 N1: Ganglio/s ipsilateral ≤6 cm *</t>
@@ -1073,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93349F43-C6E5-467C-91F1-9BFB47441F05}">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
@@ -1091,10 +1073,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
@@ -1103,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>4</v>
@@ -1114,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1</v>
@@ -1133,15 +1115,15 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1</v>
@@ -1152,15 +1134,15 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1</v>
@@ -1171,15 +1153,15 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1</v>
@@ -1190,15 +1172,15 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>1</v>
@@ -1209,58 +1191,46 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
+    <row r="8" spans="1:7" ht="7.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="D8" s="8"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
+      <c r="D9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1268,22 +1238,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>27</v>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1291,19 +1258,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1311,19 +1278,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1331,203 +1298,189 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="11" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="D16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="G16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="11" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="5"/>
+      <c r="D18" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="F18" s="5" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>68</v>
+      </c>
       <c r="F19" s="5" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="5"/>
+      <c r="D20" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="F20" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1535,99 +1488,102 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1635,236 +1591,234 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>8</v>
+        <v>50</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>8</v>
+        <v>50</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>102</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>27</v>
+      <c r="D38" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>7</v>
@@ -1873,18 +1827,18 @@
         <v>68</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>7</v>
@@ -1893,331 +1847,331 @@
         <v>69</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>8</v>
+        <v>49</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>90</v>
+        <v>70</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" s="14" t="s">
         <v>11</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>7</v>
+      <c r="B50" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>14</v>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2227,17 +2181,17 @@
       <c r="B57" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>64</v>
+      <c r="C57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2247,20 +2201,17 @@
       <c r="B58" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>8</v>
+      <c r="C58" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2270,17 +2221,17 @@
       <c r="B59" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>8</v>
+      <c r="C59" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2290,17 +2241,17 @@
       <c r="B60" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>8</v>
+      <c r="C60" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2310,17 +2261,17 @@
       <c r="B61" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>8</v>
+      <c r="C61" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2330,866 +2281,472 @@
       <c r="B62" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="D64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G62" s="2" t="s">
+    </row>
+    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="14" t="s">
+      <c r="F66" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C67" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F63" s="12" t="s">
+      <c r="D67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G63" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="5" t="s">
+    </row>
+    <row r="68" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I70" s="15"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D64" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" s="2" t="s">
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="B73" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="2" t="s">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="G76" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="5" t="s">
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="5" t="s">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="5" t="s">
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="15"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G92" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G94" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B96" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C96" s="16"/>
-      <c r="D96" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G96" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" s="12"/>
-      <c r="D98" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G98" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B99" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E99" s="18"/>
-      <c r="F99" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E100" s="12"/>
-      <c r="F100" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B101" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E101" s="18"/>
-      <c r="F101" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B102" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E102" s="12"/>
-      <c r="F102" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G102" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="11"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="11"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="11"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="11"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="11"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="11"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="11"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="11"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="7"/>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="11"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="11"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="11"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="11"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="11"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="11"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="11"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="11"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3214,66 +2771,66 @@
         <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">

--- a/tumores/Metástasis cervical de origen desconocido.xlsx
+++ b/tumores/Metástasis cervical de origen desconocido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505DD67A-604D-4843-BBCB-11939A4FD137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472B608C-C344-4016-B7BC-994145ED8F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="98">
   <si>
     <t>T</t>
   </si>
@@ -341,18 +341,6 @@
     <t>🟨 N2: Metástasis en más de 4 ganglios</t>
   </si>
   <si>
-    <t>M.Unilateral G.cervicales &lt;6cm</t>
-  </si>
-  <si>
-    <t>M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
-  </si>
-  <si>
-    <t>M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides</t>
-  </si>
-  <si>
-    <t>M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides</t>
-  </si>
-  <si>
     <t>M.Unilateral G.cervicales &gt;6cm</t>
   </si>
   <si>
@@ -363,6 +351,21 @@
   </si>
   <si>
     <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Unilateral G.cervicales &lt;6cm. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Unilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Bilateral G.retrofaringeos ≤6cm, encima del borde inferior del cricoides. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.Unilateral G.cervicales &lt;6cm, encima del  borde inferior del cricoides. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganglio ipsilateral ≤6 cm. </t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1620,7 +1623,7 @@
         <v>76</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>37</v>
@@ -2030,7 +2033,7 @@
         <v>76</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>37</v>
@@ -2056,7 +2059,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2076,7 +2079,7 @@
         <v>9</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2096,7 +2099,7 @@
         <v>9</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2116,7 +2119,7 @@
         <v>25</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2134,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2152,7 +2155,7 @@
         <v>27</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2171,7 +2174,7 @@
         <v>27</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2451,7 +2454,7 @@
         <v>76</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>37</v>

--- a/tumores/Metástasis cervical de origen desconocido.xlsx
+++ b/tumores/Metástasis cervical de origen desconocido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472B608C-C344-4016-B7BC-994145ED8F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1F60B9-7EA6-435A-9C79-5C48253FA6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="97">
   <si>
     <t>T</t>
   </si>
@@ -79,9 +79,6 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Estadio</t>
   </si>
   <si>
@@ -127,15 +124,9 @@
     <t>N2b</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>N2c</t>
   </si>
   <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>N3a</t>
   </si>
   <si>
@@ -185,9 +176,6 @@
   </si>
   <si>
     <t>Metástasis</t>
-  </si>
-  <si>
-    <t>Ninguno</t>
   </si>
   <si>
     <t>N2, N2a, N2b, N2c</t>
@@ -366,6 +354,15 @@
   </si>
   <si>
     <t xml:space="preserve">Ganglio ipsilateral ≤6 cm. </t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
 </sst>
 </file>
@@ -476,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -520,9 +517,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -534,9 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1058,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93349F43-C6E5-467C-91F1-9BFB47441F05}">
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
@@ -1076,7 +1067,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>16</v>
@@ -1099,15 +1090,15 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1</v>
@@ -1118,15 +1109,15 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1</v>
@@ -1137,15 +1128,15 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1</v>
@@ -1156,15 +1147,15 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1</v>
@@ -1175,38 +1166,28 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="D7" s="6"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>1</v>
-      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7" ht="7.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
@@ -1218,22 +1199,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1241,19 +1222,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1261,19 +1242,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1281,19 +1262,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1301,19 +1282,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -1321,20 +1302,20 @@
         <v>6</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="11" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1350,13 +1331,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -1371,19 +1352,19 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1391,19 +1372,19 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1411,19 +1392,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1431,19 +1412,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1451,19 +1432,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1471,19 +1452,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1491,13 +1472,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>9</v>
@@ -1511,22 +1492,22 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1534,19 +1515,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1554,19 +1535,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1574,19 +1555,19 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1594,19 +1575,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1614,19 +1595,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>11</v>
@@ -1637,22 +1618,22 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1660,19 +1641,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1680,19 +1661,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1700,19 +1681,19 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1720,19 +1701,19 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1740,20 +1721,20 @@
         <v>6</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1761,13 +1742,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>9</v>
@@ -1781,19 +1762,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1801,19 +1782,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1821,19 +1802,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1841,19 +1822,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1861,19 +1842,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1881,19 +1862,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1901,13 +1882,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>9</v>
@@ -1921,22 +1902,22 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1944,19 +1925,19 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1964,19 +1945,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1984,19 +1965,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2004,19 +1985,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -2024,19 +2005,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>11</v>
@@ -2047,19 +2028,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2067,19 +2048,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2087,19 +2068,19 @@
         <v>6</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2107,19 +2088,19 @@
         <v>6</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2127,17 +2108,17 @@
         <v>6</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2145,17 +2126,17 @@
         <v>6</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2163,593 +2144,286 @@
         <v>6</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
-        <v>6</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
-        <v>6</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>86</v>
+        <v>44</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
-        <v>6</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>81</v>
+      <c r="A62" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I70" s="15"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
+      <c r="A63" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B63" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F71" s="5" t="s">
+      <c r="C63" s="17"/>
+      <c r="D63" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
+      <c r="G63" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B64" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12" t="s">
+      <c r="C64" s="12"/>
+      <c r="D64" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G72" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+      <c r="G64" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F73" s="5" t="s">
+      <c r="B65" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="12" t="s">
+      <c r="G65" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B74" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12" t="s">
+      <c r="B66" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G74" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="19" t="s">
+      <c r="G66" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G80" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G82" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="11"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="11"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="11"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="11"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="11"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="11"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="11"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="11"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="18"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="14"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="11"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="11"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="11"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="11"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="11"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="11"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="11"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="11"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2777,12 +2451,12 @@
         <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
@@ -2791,162 +2465,162 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/tumores/Metástasis cervical de origen desconocido.xlsx
+++ b/tumores/Metástasis cervical de origen desconocido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1F60B9-7EA6-435A-9C79-5C48253FA6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B933C1A-5B7E-436E-852A-5E88F3A332B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -88,9 +88,6 @@
     <t>ANY</t>
   </si>
   <si>
-    <t>T0</t>
-  </si>
-  <si>
     <t>Ganglio ipsilateral ≤6 cm</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
   </si>
   <si>
     <t>N3, N3a, N3b</t>
-  </si>
-  <si>
-    <t>T0: Tumor primario no evaluable</t>
   </si>
   <si>
     <t>🟩 N1: Ganglio/s ipsilateral ≤6 cm *</t>
@@ -363,6 +357,12 @@
   </si>
   <si>
     <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>TX: Tumor primario no evaluable</t>
+  </si>
+  <si>
+    <t>TX</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1067,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>16</v>
@@ -1090,15 +1090,15 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1</v>
@@ -1109,15 +1109,15 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1</v>
@@ -1128,15 +1128,15 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1</v>
@@ -1147,15 +1147,15 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1</v>
@@ -1166,15 +1166,15 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>1</v>
@@ -1199,22 +1199,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1222,19 +1222,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1242,19 +1242,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1262,19 +1262,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1282,19 +1282,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -1302,20 +1302,20 @@
         <v>6</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="11" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1331,13 +1331,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -1352,19 +1352,19 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1372,19 +1372,19 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1392,19 +1392,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1412,19 +1412,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1432,19 +1432,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1452,19 +1452,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1472,13 +1472,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>9</v>
@@ -1492,22 +1492,22 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1515,19 +1515,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1535,19 +1535,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1555,19 +1555,19 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1575,19 +1575,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1595,19 +1595,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>11</v>
@@ -1618,22 +1618,22 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1641,19 +1641,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1661,19 +1661,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1681,19 +1681,19 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1701,19 +1701,19 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1721,20 +1721,20 @@
         <v>6</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1742,13 +1742,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>9</v>
@@ -1762,19 +1762,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1782,19 +1782,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1802,19 +1802,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1822,19 +1822,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1842,19 +1842,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1862,19 +1862,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F42" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1882,13 +1882,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>9</v>
@@ -1902,22 +1902,22 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1925,19 +1925,19 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1945,19 +1945,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1965,19 +1965,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -1985,19 +1985,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -2005,19 +2005,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>11</v>
@@ -2028,19 +2028,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2048,19 +2048,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2068,19 +2068,19 @@
         <v>6</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2088,19 +2088,19 @@
         <v>6</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2108,17 +2108,17 @@
         <v>6</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2126,17 +2126,17 @@
         <v>6</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2144,18 +2144,18 @@
         <v>6</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2163,16 +2163,16 @@
         <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2180,18 +2180,18 @@
         <v>12</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C58" s="12"/>
       <c r="D58" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2199,16 +2199,16 @@
         <v>12</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2216,18 +2216,18 @@
         <v>12</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2235,16 +2235,16 @@
         <v>12</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2252,18 +2252,18 @@
         <v>12</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -2271,18 +2271,18 @@
         <v>12</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2290,18 +2290,18 @@
         <v>12</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C64" s="12"/>
       <c r="D64" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -2309,18 +2309,18 @@
         <v>12</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E65" s="17"/>
       <c r="F65" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2328,18 +2328,18 @@
         <v>12</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2456,7 +2456,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
@@ -2470,35 +2470,35 @@
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
@@ -2507,7 +2507,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
